--- a/ModelParameters.xlsx
+++ b/ModelParameters.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/smeal/Documents/Github/D2FCSquared/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stevensmeal/Documents/MATLAB/D2FCSquared/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{826CE8D0-94E5-884C-99DE-D6F56BEB46E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{005EF827-FB05-8349-B713-C2B6415B6CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10080" yWindow="-19260" windowWidth="26840" windowHeight="15940" xr2:uid="{B0354BDC-900C-4847-8B24-4DAC70972B6C}"/>
+    <workbookView xWindow="680" yWindow="1000" windowWidth="26840" windowHeight="15940" activeTab="2" xr2:uid="{B0354BDC-900C-4847-8B24-4DAC70972B6C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="MainTextModels" sheetId="1" r:id="rId1"/>
+    <sheet name="SupplmentaryModel_IkBe" sheetId="2" r:id="rId2"/>
+    <sheet name="SupplmentaryModel_IkBb" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -37,68 +38,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="68">
-  <si>
-    <t>a1_coeff</t>
-  </si>
-  <si>
-    <t>dimensionless</t>
-  </si>
-  <si>
-    <t>b1_coeff</t>
-  </si>
-  <si>
-    <t>c1_coeff</t>
-  </si>
-  <si>
-    <t>a2_coeff</t>
-  </si>
-  <si>
-    <t>b2_coeff</t>
-  </si>
-  <si>
-    <t>c2_coeff</t>
-  </si>
-  <si>
-    <t>a3_coeff</t>
-  </si>
-  <si>
-    <t>b3_coeff</t>
-  </si>
-  <si>
-    <t>c3_coeff</t>
-  </si>
-  <si>
-    <t>a4_coeff</t>
-  </si>
-  <si>
-    <t>b4_coeff</t>
-  </si>
-  <si>
-    <t>c4_coeff</t>
-  </si>
-  <si>
-    <t>IKKSpots</t>
-  </si>
-  <si>
-    <t>TR</t>
-  </si>
-  <si>
-    <t>kv</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="88">
   <si>
     <t>ka1a</t>
   </si>
   <si>
-    <t>1/(micromole*second)</t>
-  </si>
-  <si>
     <t>kd1a</t>
   </si>
   <si>
-    <t>1/second</t>
-  </si>
-  <si>
     <t>ki1</t>
   </si>
   <si>
@@ -120,9 +67,6 @@
     <t>ka1d</t>
   </si>
   <si>
-    <t>micromole/second</t>
-  </si>
-  <si>
     <t>ps</t>
   </si>
   <si>
@@ -132,9 +76,6 @@
     <t>kdP</t>
   </si>
   <si>
-    <t>micromole</t>
-  </si>
-  <si>
     <t>h2</t>
   </si>
   <si>
@@ -241,6 +182,126 @@
   </si>
   <si>
     <t>Model Index</t>
+  </si>
+  <si>
+    <t>k_time</t>
+  </si>
+  <si>
+    <t>DelayTime</t>
+  </si>
+  <si>
+    <t>SlopeTimeDelay</t>
+  </si>
+  <si>
+    <t>rs_e</t>
+  </si>
+  <si>
+    <t>rd_e</t>
+  </si>
+  <si>
+    <t>ps_c_e</t>
+  </si>
+  <si>
+    <t>pd_n_e</t>
+  </si>
+  <si>
+    <t>in_e</t>
+  </si>
+  <si>
+    <t>ex_e</t>
+  </si>
+  <si>
+    <t>a_c_en</t>
+  </si>
+  <si>
+    <t>d_c_en</t>
+  </si>
+  <si>
+    <t>f_a_n_en</t>
+  </si>
+  <si>
+    <t>f_d_n_en</t>
+  </si>
+  <si>
+    <t>a_n_en</t>
+  </si>
+  <si>
+    <t>d_n_en</t>
+  </si>
+  <si>
+    <t>pd_c_2en</t>
+  </si>
+  <si>
+    <t>ex_2en</t>
+  </si>
+  <si>
+    <t>kc1e</t>
+  </si>
+  <si>
+    <t>kt1e</t>
+  </si>
+  <si>
+    <t>kc2e</t>
+  </si>
+  <si>
+    <t>kt2e</t>
+  </si>
+  <si>
+    <t>BestParamSet</t>
+  </si>
+  <si>
+    <t>rs_b</t>
+  </si>
+  <si>
+    <t>rd_b</t>
+  </si>
+  <si>
+    <t>ps_c_b</t>
+  </si>
+  <si>
+    <t>pd_n_b</t>
+  </si>
+  <si>
+    <t>in_b</t>
+  </si>
+  <si>
+    <t>ex_b</t>
+  </si>
+  <si>
+    <t>a_c_bn</t>
+  </si>
+  <si>
+    <t>d_c_bn</t>
+  </si>
+  <si>
+    <t>a_n_bn</t>
+  </si>
+  <si>
+    <t>d_n_bn</t>
+  </si>
+  <si>
+    <t>f_a_n_bn</t>
+  </si>
+  <si>
+    <t>f_d_n_bn</t>
+  </si>
+  <si>
+    <t>pd_c_2bn</t>
+  </si>
+  <si>
+    <t>ex_2bn</t>
+  </si>
+  <si>
+    <t>kc1b</t>
+  </si>
+  <si>
+    <t>kt1b</t>
+  </si>
+  <si>
+    <t>kc2b</t>
+  </si>
+  <si>
+    <t>kt2b</t>
   </si>
 </sst>
 </file>
@@ -625,22 +686,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="C1" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="D1" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="E1" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="F1" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -648,7 +709,7 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>0.58537037661186297</v>
@@ -668,7 +729,7 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C3">
         <v>0.05</v>
@@ -688,7 +749,7 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C4">
         <v>5.40346181007368E-3</v>
@@ -708,7 +769,7 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1">
         <v>9.6566966547358395E-5</v>
@@ -728,7 +789,7 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>4.2495263604071E-2</v>
@@ -748,7 +809,7 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C7">
         <v>2.6252840282952401E-2</v>
@@ -768,7 +829,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C8" s="1">
         <v>1E-14</v>
@@ -788,7 +849,7 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C9" s="1">
         <v>1E-14</v>
@@ -808,7 +869,7 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C10">
         <v>7.0701868834476304E-4</v>
@@ -828,7 +889,7 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C11">
         <v>7950.54601491426</v>
@@ -848,7 +909,7 @@
         <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -868,7 +929,7 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C13">
         <v>3.1623000000000001</v>
@@ -888,7 +949,7 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C14">
         <v>1.500039277643</v>
@@ -908,7 +969,7 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="C15">
         <v>1.03392964193572</v>
@@ -928,7 +989,7 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C16">
         <v>1.31976626403725E-2</v>
@@ -948,7 +1009,7 @@
         <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1">
         <v>6.6839147418279002E-5</v>
@@ -968,7 +1029,7 @@
         <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C18">
         <v>5.0000000000000001E-4</v>
@@ -988,7 +1049,7 @@
         <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C19">
         <v>8.3534306976273606E-2</v>
@@ -1008,7 +1069,7 @@
         <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C20">
         <v>6.6375602837135603E-3</v>
@@ -1028,7 +1089,7 @@
         <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C21">
         <v>2.4568865315407599E-3</v>
@@ -1048,7 +1109,7 @@
         <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C22" s="1">
         <v>2.1999999999999999E-5</v>
@@ -1068,7 +1129,7 @@
         <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C23" s="1">
         <v>2.4094562521491999E-6</v>
@@ -1088,7 +1149,7 @@
         <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="C24">
         <v>1.15582265380659E-2</v>
@@ -1108,7 +1169,7 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C25" s="1">
         <v>6.4642810689536899E-5</v>
@@ -1128,7 +1189,7 @@
         <v>40</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C26">
         <v>1.8E-3</v>
@@ -1148,7 +1209,7 @@
         <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C27">
         <v>15.253786867615499</v>
@@ -1168,7 +1229,7 @@
         <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="C28">
         <v>2</v>
@@ -1188,7 +1249,7 @@
         <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C29">
         <v>6.6809019708135603E-2</v>
@@ -1208,7 +1269,7 @@
         <v>44</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C30" s="1">
         <v>6.8524087986003297E-8</v>
@@ -1228,7 +1289,7 @@
         <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C31">
         <v>2.9999999999999997E-4</v>
@@ -1248,7 +1309,7 @@
         <v>46</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C32">
         <v>0.5</v>
@@ -1268,7 +1329,7 @@
         <v>47</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C33">
         <v>1.01781819083976E-2</v>
@@ -1288,7 +1349,7 @@
         <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="C34" s="1">
         <v>4.2899999999999999E-5</v>
@@ -1308,7 +1369,7 @@
         <v>49</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="C35" s="1">
         <v>1.9999999999999999E-7</v>
@@ -1328,7 +1389,7 @@
         <v>50</v>
       </c>
       <c r="B36" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C36">
         <v>0.99792105619231897</v>
@@ -1348,7 +1409,7 @@
         <v>51</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="C37">
         <v>4.0000000000000002E-4</v>
@@ -1368,7 +1429,7 @@
         <v>52</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="C38">
         <v>0.5</v>
@@ -1388,7 +1449,7 @@
         <v>53</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="C39">
         <v>4.4999999999999997E-3</v>
@@ -1408,7 +1469,7 @@
         <v>54</v>
       </c>
       <c r="B40" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="C40">
         <v>0.49978634534456601</v>
@@ -1428,7 +1489,7 @@
         <v>55</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C41">
         <v>5.7962439055050498E-3</v>
@@ -1448,7 +1509,7 @@
         <v>56</v>
       </c>
       <c r="B42" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="C42">
         <v>0.40710489032555802</v>
@@ -1468,7 +1529,7 @@
         <v>57</v>
       </c>
       <c r="B43" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="C43">
         <v>1.2738075389777501E-4</v>
@@ -1490,805 +1551,1220 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2F67590-9950-8441-907B-76D094A38F91}">
-  <dimension ref="B1:E57"/>
+  <dimension ref="A1:C56"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>1.20221</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>1.5508299999999999E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>5.1995000000000003E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>0.99477700000000002</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>1.09347E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1E-14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1E-14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11">
+        <v>3.5427200000000001E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12">
+        <v>2.8522600000000001E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13">
+        <v>1.1899499999999999E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.1999999999999999E-5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1.33412E-7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16">
+        <v>4.1906400000000003E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17">
+        <v>8.1110699999999997E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>32</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18">
+        <v>1.8E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>33</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19">
+        <v>24.996300000000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>34</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>35</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21">
+        <v>0.68102499999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>36</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="1">
+        <v>5.0496399999999999E-8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>37</v>
+      </c>
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23">
+        <v>2.9999999999999997E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>38</v>
+      </c>
+      <c r="B24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>39</v>
+      </c>
+      <c r="B25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25">
+        <v>1.97343E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>40</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="1">
+        <v>4.2899999999999999E-5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>41</v>
+      </c>
+      <c r="B27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1.9999999999999999E-7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>42</v>
+      </c>
+      <c r="B28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28">
+        <v>3.4720500000000001E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>43</v>
+      </c>
+      <c r="B29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29">
+        <v>4.0000000000000002E-4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>44</v>
+      </c>
+      <c r="B30" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>45</v>
+      </c>
+      <c r="B31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31">
+        <v>4.4999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>46</v>
+      </c>
+      <c r="B32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32">
+        <v>0.49951099999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>47</v>
+      </c>
+      <c r="B33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="1">
+        <v>2.64199E-6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>48</v>
+      </c>
+      <c r="B34" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34">
+        <v>9.1587000000000005E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>49</v>
+      </c>
+      <c r="B35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35">
+        <v>4.3843700000000003E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>50</v>
+      </c>
+      <c r="B36" t="s">
+        <v>48</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>51</v>
+      </c>
+      <c r="B37" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>52</v>
+      </c>
+      <c r="B38" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38">
+        <v>9.9899000000000004</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>53</v>
+      </c>
+      <c r="B39" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="1">
+        <v>9.9232199999999996E-8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>54</v>
+      </c>
+      <c r="B40" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40">
+        <v>2.9999999999999997E-4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>55</v>
+      </c>
+      <c r="B41" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>56</v>
+      </c>
+      <c r="B42" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>57</v>
+      </c>
+      <c r="B43" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43">
+        <v>2.9294799999999999E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>58</v>
+      </c>
+      <c r="B44" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" s="1">
+        <v>5.2373700000000003E-5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>59</v>
+      </c>
+      <c r="B45" t="s">
+        <v>57</v>
+      </c>
+      <c r="C45">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>60</v>
+      </c>
+      <c r="B46" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>61</v>
+      </c>
+      <c r="B47" t="s">
+        <v>59</v>
+      </c>
+      <c r="C47">
+        <v>0.14008300000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>62</v>
+      </c>
+      <c r="B48" t="s">
+        <v>60</v>
+      </c>
+      <c r="C48">
+        <v>1.41041E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>63</v>
+      </c>
+      <c r="B49" t="s">
+        <v>61</v>
+      </c>
+      <c r="C49" s="1">
+        <v>1E-14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>64</v>
+      </c>
+      <c r="B50" t="s">
+        <v>62</v>
+      </c>
+      <c r="C50" s="1">
+        <v>1E-14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>65</v>
+      </c>
+      <c r="B51" t="s">
+        <v>63</v>
+      </c>
+      <c r="C51" s="1">
+        <v>2.1999999999999999E-5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>66</v>
+      </c>
+      <c r="B52" t="s">
+        <v>64</v>
+      </c>
+      <c r="C52">
+        <v>7.10171E-4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>67</v>
+      </c>
+      <c r="B53" t="s">
+        <v>65</v>
+      </c>
+      <c r="C53">
+        <v>9.09161E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>68</v>
+      </c>
+      <c r="B54" t="s">
+        <v>66</v>
+      </c>
+      <c r="C54">
+        <v>1.89795E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>69</v>
+      </c>
+      <c r="B55" t="s">
+        <v>67</v>
+      </c>
+      <c r="C55">
+        <v>1.7960899999999998E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>70</v>
+      </c>
+      <c r="B56" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56">
+        <v>5.9801400000000001E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A65B355F-A6DF-B94E-8711-24FCE44D5088}">
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>1.8398699999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1">
-        <v>-4088.41</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B2">
+      <c r="C3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C4">
+        <v>8.8673099999999998E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1">
+        <v>5.7397899999999998E-6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>1.0166E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>1.0011000000000001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1E-14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1E-14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>25</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11">
+        <v>1.0139599999999999E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="1">
+        <v>6.8322800000000003E-5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13">
+        <v>3.1906399999999998E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>28</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.1999999999999999E-5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1.4543E-5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16">
+        <v>1.03141E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17">
+        <v>1.15438E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>32</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18">
+        <v>1.8E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>33</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19">
+        <v>24.999400000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>34</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20">
         <v>2</v>
       </c>
-      <c r="D2">
-        <v>1930.29</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>652.60500000000002</v>
-      </c>
-      <c r="E3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>120.375</v>
-      </c>
-      <c r="E4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B5">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>1016.05</v>
-      </c>
-      <c r="E5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>349.77</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B7">
-        <v>7</v>
-      </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7">
-        <v>4256.33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B8">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8">
-        <v>1919.75</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B9">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9">
-        <v>665.24900000000002</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B10">
-        <v>10</v>
-      </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10">
-        <v>66.207400000000007</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B11">
-        <v>11</v>
-      </c>
-      <c r="C11" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11">
-        <v>3745.46</v>
-      </c>
-      <c r="E11" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B12">
-        <v>12</v>
-      </c>
-      <c r="C12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12">
-        <v>2162.23</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B13">
-        <v>13</v>
-      </c>
-      <c r="C13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B14">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B15">
-        <v>15</v>
-      </c>
-      <c r="C15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15">
-        <v>3.3</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B16">
-        <v>16</v>
-      </c>
-      <c r="C16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16">
-        <v>0.58536999999999995</v>
-      </c>
-      <c r="E16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B17">
-        <v>17</v>
-      </c>
-      <c r="C17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>35</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21">
+        <v>6.5025299999999994E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>36</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="1">
+        <v>7.0749200000000005E-8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>37</v>
+      </c>
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23">
+        <v>2.9999999999999997E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>38</v>
+      </c>
+      <c r="B24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>39</v>
+      </c>
+      <c r="B25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25">
+        <v>0.98132600000000003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>40</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="1">
+        <v>4.2899999999999999E-5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>41</v>
+      </c>
+      <c r="B27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1.9999999999999999E-7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>42</v>
+      </c>
+      <c r="B28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28">
+        <v>3.78362E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>43</v>
+      </c>
+      <c r="B29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29">
+        <v>4.0000000000000002E-4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>44</v>
+      </c>
+      <c r="B30" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>45</v>
+      </c>
+      <c r="B31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31">
+        <v>4.4999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>46</v>
+      </c>
+      <c r="B32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32">
+        <v>0.49989299999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>47</v>
+      </c>
+      <c r="B33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33">
+        <v>5.7551599999999996E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>48</v>
+      </c>
+      <c r="B34" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34">
+        <v>0.499921</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35">
+        <v>49</v>
+      </c>
+      <c r="B35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35">
+        <v>3.9705300000000002E-4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36">
+        <v>50</v>
+      </c>
+      <c r="B36" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="1">
+        <v>5.2623299999999997E-8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37">
+        <v>51</v>
+      </c>
+      <c r="B37" t="s">
+        <v>71</v>
+      </c>
+      <c r="C37">
+        <v>2.9999999999999997E-4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38">
+        <v>52</v>
+      </c>
+      <c r="B38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39">
+        <v>53</v>
+      </c>
+      <c r="B39" t="s">
+        <v>73</v>
+      </c>
+      <c r="C39">
+        <v>5.0000000000000001E-4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40">
+        <v>54</v>
+      </c>
+      <c r="B40" t="s">
+        <v>74</v>
+      </c>
+      <c r="C40">
+        <v>2.9330699999999999E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41">
+        <v>55</v>
+      </c>
+      <c r="B41" t="s">
+        <v>75</v>
+      </c>
+      <c r="C41" s="1">
+        <v>6.3650600000000003E-5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42">
+        <v>56</v>
+      </c>
+      <c r="B42" t="s">
+        <v>76</v>
+      </c>
+      <c r="C42">
+        <v>1.05872E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>57</v>
+      </c>
+      <c r="B43" t="s">
+        <v>77</v>
+      </c>
+      <c r="C43">
         <v>0.05</v>
       </c>
-      <c r="E17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B18">
-        <v>18</v>
-      </c>
-      <c r="C18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18">
-        <v>5.4034599999999997E-3</v>
-      </c>
-      <c r="E18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B19">
-        <v>19</v>
-      </c>
-      <c r="C19" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="1">
-        <v>9.6566999999999999E-5</v>
-      </c>
-      <c r="E19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B20">
-        <v>20</v>
-      </c>
-      <c r="C20" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20">
-        <v>4.24953E-2</v>
-      </c>
-      <c r="E20" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B21">
-        <v>21</v>
-      </c>
-      <c r="C21" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21">
-        <v>2.62528E-2</v>
-      </c>
-      <c r="E21" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B22">
-        <v>22</v>
-      </c>
-      <c r="C22" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" s="1">
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>58</v>
+      </c>
+      <c r="B44" t="s">
+        <v>78</v>
+      </c>
+      <c r="C44" s="1">
         <v>1E-14</v>
       </c>
-      <c r="E22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B23">
-        <v>23</v>
-      </c>
-      <c r="C23" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="1">
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>59</v>
+      </c>
+      <c r="B45" t="s">
+        <v>79</v>
+      </c>
+      <c r="C45" s="1">
         <v>1E-14</v>
       </c>
-      <c r="E23" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B24">
-        <v>24</v>
-      </c>
-      <c r="C24" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24">
-        <v>7.0701900000000003E-4</v>
-      </c>
-      <c r="E24" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B25">
-        <v>25</v>
-      </c>
-      <c r="C25" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25">
-        <v>7950.55</v>
-      </c>
-      <c r="E25" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B26">
-        <v>26</v>
-      </c>
-      <c r="C26" t="s">
-        <v>29</v>
-      </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-      <c r="E26" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B27">
-        <v>27</v>
-      </c>
-      <c r="C27" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27">
-        <v>3.1623000000000001</v>
-      </c>
-      <c r="E27" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B28">
-        <v>28</v>
-      </c>
-      <c r="C28" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28">
-        <v>1.50004</v>
-      </c>
-      <c r="E28" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B29">
-        <v>29</v>
-      </c>
-      <c r="C29" t="s">
-        <v>33</v>
-      </c>
-      <c r="D29">
-        <v>1.03393</v>
-      </c>
-      <c r="E29" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B30">
-        <v>30</v>
-      </c>
-      <c r="C30" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30">
-        <v>1.31977E-2</v>
-      </c>
-      <c r="E30" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B31">
-        <v>31</v>
-      </c>
-      <c r="C31" t="s">
-        <v>35</v>
-      </c>
-      <c r="D31" s="1">
-        <v>6.6839099999999995E-5</v>
-      </c>
-      <c r="E31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B32">
-        <v>32</v>
-      </c>
-      <c r="C32" t="s">
-        <v>36</v>
-      </c>
-      <c r="D32">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="E32" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B33">
-        <v>33</v>
-      </c>
-      <c r="C33" t="s">
-        <v>37</v>
-      </c>
-      <c r="D33">
-        <v>8.3534300000000006E-2</v>
-      </c>
-      <c r="E33" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B34">
-        <v>34</v>
-      </c>
-      <c r="C34" t="s">
-        <v>38</v>
-      </c>
-      <c r="D34">
-        <v>6.6375599999999998E-3</v>
-      </c>
-      <c r="E34" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B35">
-        <v>35</v>
-      </c>
-      <c r="C35" t="s">
-        <v>39</v>
-      </c>
-      <c r="D35">
-        <v>2.4568900000000002E-3</v>
-      </c>
-      <c r="E35" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B36">
-        <v>36</v>
-      </c>
-      <c r="C36" t="s">
-        <v>40</v>
-      </c>
-      <c r="D36" s="1">
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>60</v>
+      </c>
+      <c r="B46" t="s">
+        <v>80</v>
+      </c>
+      <c r="C46">
+        <v>4.7836999999999998E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>61</v>
+      </c>
+      <c r="B47" t="s">
+        <v>81</v>
+      </c>
+      <c r="C47">
+        <v>1.05612E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>62</v>
+      </c>
+      <c r="B48" t="s">
+        <v>82</v>
+      </c>
+      <c r="C48" s="1">
         <v>2.1999999999999999E-5</v>
       </c>
-      <c r="E36" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B37">
-        <v>37</v>
-      </c>
-      <c r="C37" t="s">
-        <v>41</v>
-      </c>
-      <c r="D37" s="1">
-        <v>2.4094600000000001E-6</v>
-      </c>
-      <c r="E37" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B38">
-        <v>38</v>
-      </c>
-      <c r="C38" t="s">
-        <v>42</v>
-      </c>
-      <c r="D38">
-        <v>1.1558199999999999E-2</v>
-      </c>
-      <c r="E38" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B39">
-        <v>39</v>
-      </c>
-      <c r="C39" t="s">
-        <v>43</v>
-      </c>
-      <c r="D39" s="1">
-        <v>6.4642799999999997E-5</v>
-      </c>
-      <c r="E39" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B40">
-        <v>40</v>
-      </c>
-      <c r="C40" t="s">
-        <v>44</v>
-      </c>
-      <c r="D40">
-        <v>1.8E-3</v>
-      </c>
-      <c r="E40" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B41">
-        <v>41</v>
-      </c>
-      <c r="C41" t="s">
-        <v>45</v>
-      </c>
-      <c r="D41">
-        <v>15.2538</v>
-      </c>
-      <c r="E41" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B42">
-        <v>42</v>
-      </c>
-      <c r="C42" t="s">
-        <v>46</v>
-      </c>
-      <c r="D42">
-        <v>2</v>
-      </c>
-      <c r="E42" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B43">
-        <v>43</v>
-      </c>
-      <c r="C43" t="s">
-        <v>47</v>
-      </c>
-      <c r="D43">
-        <v>6.6808999999999993E-2</v>
-      </c>
-      <c r="E43" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B44">
-        <v>44</v>
-      </c>
-      <c r="C44" t="s">
-        <v>48</v>
-      </c>
-      <c r="D44" s="1">
-        <v>6.8524100000000004E-8</v>
-      </c>
-      <c r="E44" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B45">
-        <v>45</v>
-      </c>
-      <c r="C45" t="s">
-        <v>49</v>
-      </c>
-      <c r="D45">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="E45" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B46">
-        <v>46</v>
-      </c>
-      <c r="C46" t="s">
-        <v>50</v>
-      </c>
-      <c r="D46">
-        <v>0.5</v>
-      </c>
-      <c r="E46" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B47">
-        <v>47</v>
-      </c>
-      <c r="C47" t="s">
-        <v>51</v>
-      </c>
-      <c r="D47">
-        <v>1.01782E-2</v>
-      </c>
-      <c r="E47" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B48">
-        <v>48</v>
-      </c>
-      <c r="C48" t="s">
-        <v>52</v>
-      </c>
-      <c r="D48" s="1">
-        <v>4.2899999999999999E-5</v>
-      </c>
-      <c r="E48" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B49">
-        <v>49</v>
-      </c>
-      <c r="C49" t="s">
-        <v>53</v>
-      </c>
-      <c r="D49" s="1">
-        <v>1.9999999999999999E-7</v>
-      </c>
-      <c r="E49" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B50">
-        <v>50</v>
-      </c>
-      <c r="C50" t="s">
-        <v>54</v>
-      </c>
-      <c r="D50">
-        <v>0.99792099999999995</v>
-      </c>
-      <c r="E50" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B51">
-        <v>51</v>
-      </c>
-      <c r="C51" t="s">
-        <v>55</v>
-      </c>
-      <c r="D51">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="E51" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B52">
-        <v>52</v>
-      </c>
-      <c r="C52" t="s">
-        <v>56</v>
-      </c>
-      <c r="D52">
-        <v>0.5</v>
-      </c>
-      <c r="E52" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B53">
-        <v>53</v>
-      </c>
-      <c r="C53" t="s">
-        <v>57</v>
-      </c>
-      <c r="D53">
-        <v>4.4999999999999997E-3</v>
-      </c>
-      <c r="E53" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B54">
-        <v>54</v>
-      </c>
-      <c r="C54" t="s">
-        <v>58</v>
-      </c>
-      <c r="D54">
-        <v>0.49978600000000001</v>
-      </c>
-      <c r="E54" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B55">
-        <v>55</v>
-      </c>
-      <c r="C55" t="s">
-        <v>59</v>
-      </c>
-      <c r="D55">
-        <v>5.7962400000000002E-3</v>
-      </c>
-      <c r="E55" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B56">
-        <v>56</v>
-      </c>
-      <c r="C56" t="s">
-        <v>60</v>
-      </c>
-      <c r="D56">
-        <v>0.40710499999999999</v>
-      </c>
-      <c r="E56" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B57">
-        <v>57</v>
-      </c>
-      <c r="C57" t="s">
-        <v>61</v>
-      </c>
-      <c r="D57">
-        <v>1.2738100000000001E-4</v>
-      </c>
-      <c r="E57" t="s">
-        <v>19</v>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>63</v>
+      </c>
+      <c r="B49" t="s">
+        <v>83</v>
+      </c>
+      <c r="C49">
+        <v>2.0901499999999998E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>64</v>
+      </c>
+      <c r="B50" t="s">
+        <v>84</v>
+      </c>
+      <c r="C50">
+        <v>0.36925200000000002</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>65</v>
+      </c>
+      <c r="B51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C51" s="1">
+        <v>2.4084300000000001E-6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>66</v>
+      </c>
+      <c r="B52" t="s">
+        <v>86</v>
+      </c>
+      <c r="C52">
+        <v>1.42288E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>67</v>
+      </c>
+      <c r="B53" t="s">
+        <v>87</v>
+      </c>
+      <c r="C53">
+        <v>5.9952499999999997E-3</v>
       </c>
     </row>
   </sheetData>
